--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_atacama.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-06 19:42</t>
+    <t xml:space="preserve">2026-09-09 22:29</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_atacama.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-09 22:29</t>
+    <t xml:space="preserve">2026-09-12 19:45</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_atacama.xlsx
@@ -39,27 +39,27 @@
     <t xml:space="preserve">Caldera</t>
   </si>
   <si>
+    <t xml:space="preserve">Huasco</t>
+  </si>
+  <si>
     <t xml:space="preserve">Vallenar</t>
   </si>
   <si>
+    <t xml:space="preserve">Freirina</t>
+  </si>
+  <si>
     <t xml:space="preserve">Alto del Carmen</t>
   </si>
   <si>
-    <t xml:space="preserve">Freirina</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Huasco</t>
-  </si>
-  <si>
     <t xml:space="preserve">Chañaral</t>
   </si>
   <si>
+    <t xml:space="preserve">Diego de Almagro</t>
+  </si>
+  <si>
     <t xml:space="preserve">Tierra Amarilla</t>
   </si>
   <si>
-    <t xml:space="preserve">Diego de Almagro</t>
-  </si>
-  <si>
     <t xml:space="preserve">Copiapó</t>
   </si>
   <si>
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-12 19:45</t>
+    <t xml:space="preserve">2026-09-24 00:23</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -502,7 +502,7 @@
         <v>2022</v>
       </c>
       <c r="E2" s="2" t="n">
-        <v>846</v>
+        <v>652</v>
       </c>
     </row>
     <row r="3">
@@ -513,13 +513,13 @@
         <v>7</v>
       </c>
       <c r="C3" s="2" t="n">
-        <v>3301</v>
+        <v>3304</v>
       </c>
       <c r="D3" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E3" s="2" t="n">
-        <v>307</v>
+        <v>506</v>
       </c>
     </row>
     <row r="4">
@@ -530,13 +530,13 @@
         <v>8</v>
       </c>
       <c r="C4" s="2" t="n">
-        <v>3302</v>
+        <v>3301</v>
       </c>
       <c r="D4" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E4" s="2" t="n">
-        <v>220</v>
+        <v>261</v>
       </c>
     </row>
     <row r="5">
@@ -553,7 +553,7 @@
         <v>2022</v>
       </c>
       <c r="E5" s="2" t="n">
-        <v>212</v>
+        <v>254</v>
       </c>
     </row>
     <row r="6">
@@ -564,13 +564,13 @@
         <v>10</v>
       </c>
       <c r="C6" s="2" t="n">
-        <v>3304</v>
+        <v>3302</v>
       </c>
       <c r="D6" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E6" s="2" t="n">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="7">
@@ -587,7 +587,7 @@
         <v>2022</v>
       </c>
       <c r="E7" s="2" t="n">
-        <v>-348</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8">
@@ -598,13 +598,13 @@
         <v>12</v>
       </c>
       <c r="C8" s="2" t="n">
-        <v>3103</v>
+        <v>3202</v>
       </c>
       <c r="D8" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E8" s="2" t="n">
-        <v>-688</v>
+        <v>80</v>
       </c>
     </row>
     <row r="9">
@@ -615,13 +615,13 @@
         <v>13</v>
       </c>
       <c r="C9" s="2" t="n">
-        <v>3202</v>
+        <v>3103</v>
       </c>
       <c r="D9" s="2" t="n">
         <v>2022</v>
       </c>
       <c r="E9" s="2" t="n">
-        <v>-1139</v>
+        <v>-409</v>
       </c>
     </row>
     <row r="10">
@@ -638,7 +638,7 @@
         <v>2022</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-3356</v>
+        <v>-510</v>
       </c>
     </row>
   </sheetData>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_atacama.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-24 00:23</t>
+    <t xml:space="preserve">2026-09-27 22:12</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_atacama.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-27 22:12</t>
+    <t xml:space="preserve">2026-10-01 20:53</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_atacama.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-01 20:53</t>
+    <t xml:space="preserve">2026-10-02 13:17</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>

--- a/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_atacama.xlsx
+++ b/output/graficos_dimensiones/comunal_m_saldomigr_a_2022_atacama.xlsx
@@ -69,7 +69,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-10-02 13:17</t>
+    <t xml:space="preserve">2026-10-05 07:56</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
